--- a/01 基本設計/基本設計書.xlsx
+++ b/01 基本設計/基本設計書.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\springboot\translacat-docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\springboot\translacat-docs\01 基本設計\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA945D8-F876-4C37-957F-8893103ACFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C3F26E-F736-40ED-8993-64DC4207285C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="353">
   <si>
     <t>TranslaCat / FE + Spring Boot + FastAPI</t>
   </si>
@@ -1331,6 +1331,23 @@
     </rPh>
     <rPh sb="40" eb="42">
       <t>サンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定</t>
+    <rPh sb="0" eb="2">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>閲覧履歴</t>
+    <rPh sb="0" eb="2">
+      <t>エツラン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>リレキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1578,29 +1595,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1611,9 +1653,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1630,34 +1669,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2006,433 +2022,433 @@
   <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="15" width="14" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="3"/>
+    <col min="1" max="15" width="14" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.95" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
     </row>
     <row r="2" spans="1:15" ht="27.95" customHeight="1">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
     </row>
     <row r="3" spans="1:15" ht="27.95" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
     </row>
     <row r="4" spans="1:15" ht="27.95" customHeight="1"/>
     <row r="5" spans="1:15" ht="27.95" customHeight="1"/>
     <row r="6" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
     </row>
     <row r="7" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
     </row>
     <row r="8" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
     </row>
     <row r="9" spans="1:15" ht="27.95" customHeight="1"/>
     <row r="10" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
     </row>
     <row r="12" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
     </row>
     <row r="13" spans="1:15" ht="27.95" customHeight="1"/>
     <row r="14" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
     </row>
     <row r="15" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
     </row>
     <row r="16" spans="1:15" ht="27.95" customHeight="1">
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
     </row>
     <row r="17" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
     </row>
     <row r="18" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
     </row>
     <row r="19" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
     </row>
     <row r="20" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
     </row>
     <row r="21" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
     </row>
     <row r="22" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
     </row>
     <row r="23" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
     </row>
     <row r="24" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
     </row>
     <row r="25" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
     </row>
     <row r="26" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
     </row>
     <row r="27" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
     </row>
     <row r="28" spans="2:14" ht="27.95" customHeight="1"/>
     <row r="29" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
     </row>
     <row r="30" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
     </row>
     <row r="31" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
     </row>
     <row r="32" spans="2:14" ht="27.95" customHeight="1">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
     </row>
     <row r="33" ht="27.95" customHeight="1"/>
     <row r="34" ht="27.95" customHeight="1"/>
@@ -2454,47 +2470,47 @@
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="14" width="12" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3"/>
+    <col min="1" max="14" width="12" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1"/>
     <row r="4" spans="1:14" ht="24" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="5" t="s">
         <v>350</v>
       </c>
     </row>
@@ -2510,30 +2526,30 @@
     <row r="14" spans="1:14" ht="24" customHeight="1"/>
     <row r="15" spans="1:14" ht="24" customHeight="1"/>
     <row r="16" spans="1:14" ht="24" customHeight="1"/>
-    <row r="17" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="18" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="19" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="20" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="21" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="22" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="23" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="24" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="25" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="26" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="27" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="28" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="29" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="30" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="31" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="32" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="33" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="34" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="35" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="36" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="37" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="38" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="39" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="40" s="3" customFormat="1" ht="24" customHeight="1"/>
+    <row r="17" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="18" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="19" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="20" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="21" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="22" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="23" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="24" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="25" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="26" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="27" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="28" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="29" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="30" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="31" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="32" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="33" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="34" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="35" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="36" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="37" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="38" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="39" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="40" s="1" customFormat="1" ht="24" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N2"/>
@@ -2548,47 +2564,47 @@
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="14" width="12" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3"/>
+    <col min="1" max="14" width="12" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1"/>
     <row r="4" spans="1:14" ht="24" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="5" t="s">
         <v>349</v>
       </c>
     </row>
@@ -2604,30 +2620,30 @@
     <row r="14" spans="1:14" ht="24" customHeight="1"/>
     <row r="15" spans="1:14" ht="24" customHeight="1"/>
     <row r="16" spans="1:14" ht="24" customHeight="1"/>
-    <row r="17" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="18" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="19" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="20" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="21" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="22" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="23" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="24" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="25" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="26" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="27" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="28" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="29" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="30" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="31" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="32" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="33" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="34" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="35" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="36" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="37" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="38" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="39" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="40" s="3" customFormat="1" ht="24" customHeight="1"/>
+    <row r="17" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="18" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="19" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="20" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="21" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="22" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="23" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="24" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="25" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="26" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="27" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="28" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="29" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="30" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="31" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="32" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="33" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="34" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="35" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="36" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="37" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="38" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="39" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="40" s="1" customFormat="1" ht="24" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N2"/>
@@ -2639,81 +2655,69 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="20" style="3" customWidth="1"/>
-    <col min="2" max="2" width="104.125" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="20" style="1" customWidth="1"/>
+    <col min="2" max="2" width="104.125" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A1" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="26" t="s">
+      <c r="B1" s="27"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="37.5">
-      <c r="A5" s="27" t="s">
+    <row r="5" spans="1:2" ht="37.5">
+      <c r="A5" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="10" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="27" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="10" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="27" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="10" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="27" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="12" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="27" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="10" t="s">
         <v>306</v>
       </c>
     </row>
@@ -2731,94 +2735,94 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" customWidth="1"/>
-    <col min="2" max="3" width="14" style="3" customWidth="1"/>
-    <col min="4" max="4" width="60" style="3" customWidth="1"/>
-    <col min="5" max="5" width="26" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="3" width="14" style="1" customWidth="1"/>
+    <col min="4" max="4" width="60" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="12"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="21"/>
     </row>
     <row r="5" spans="1:8" ht="25.5" customHeight="1">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="16"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="11">
         <v>46097</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="16"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2837,178 +2841,178 @@
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="14" width="12" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3"/>
+    <col min="1" max="14" width="12" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
     </row>
     <row r="13" spans="1:14" ht="24" customHeight="1">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="5" t="s">
         <v>309</v>
       </c>
     </row>
@@ -3055,269 +3059,269 @@
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="12" style="3" customWidth="1"/>
-    <col min="2" max="3" width="20" style="3" customWidth="1"/>
-    <col min="4" max="4" width="54.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="39.75" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="3" width="20" style="1" customWidth="1"/>
+    <col min="4" max="4" width="54.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="39.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="2" spans="1:6" ht="13.5" customHeight="1">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="4" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="4" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="13" t="s">
+      <c r="B14" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="4" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="13" t="s">
+      <c r="B15" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="4" t="s">
         <v>332</v>
       </c>
     </row>
@@ -3335,680 +3339,680 @@
   <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" customWidth="1"/>
-    <col min="2" max="2" width="26" style="3" customWidth="1"/>
-    <col min="3" max="3" width="22" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="65.5" style="3" customWidth="1"/>
-    <col min="6" max="7" width="35.375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="37.875" style="3" customWidth="1"/>
-    <col min="9" max="10" width="24" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="1" customWidth="1"/>
+    <col min="4" max="4" width="50.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="65.5" style="1" customWidth="1"/>
+    <col min="6" max="7" width="35.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="37.875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="24" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="J7" s="7" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="22" t="s">
+      <c r="J8" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="22" t="s">
+      <c r="J9" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="J10" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J11" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="J15" s="22" t="s">
+      <c r="J15" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="30">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="I17" s="22" t="s">
+      <c r="I17" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J17" s="22" t="s">
+      <c r="J17" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="I18" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J18" s="22" t="s">
+      <c r="J18" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="I19" s="22" t="s">
+      <c r="I19" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J19" s="22" t="s">
+      <c r="J19" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="I20" s="22" t="s">
+      <c r="I20" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J20" s="22" t="s">
+      <c r="J20" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="I21" s="22" t="s">
+      <c r="I21" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="J21" s="22" t="s">
+      <c r="J21" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="I22" s="22" t="s">
+      <c r="I22" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="7" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="I23" s="22" t="s">
+      <c r="I23" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J23" s="22" t="s">
+      <c r="J23" s="7" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4026,457 +4030,457 @@
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" customWidth="1"/>
-    <col min="2" max="2" width="27.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12" style="3" customWidth="1"/>
-    <col min="4" max="4" width="89.875" style="3" customWidth="1"/>
-    <col min="5" max="8" width="14" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="1" customWidth="1"/>
+    <col min="4" max="4" width="89.875" style="1" customWidth="1"/>
+    <col min="5" max="8" width="14" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="6" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4492,173 +4496,173 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" customWidth="1"/>
-    <col min="2" max="2" width="34.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="54.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30" style="3" customWidth="1"/>
-    <col min="5" max="6" width="18" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="54.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30" style="1" customWidth="1"/>
+    <col min="5" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="3" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="33">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" ht="33">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" ht="33">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" ht="33">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4675,47 +4679,47 @@
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="14" width="12" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3"/>
+    <col min="1" max="14" width="12" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1"/>
     <row r="4" spans="1:14" ht="24" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="5" t="s">
         <v>347</v>
       </c>
     </row>
@@ -4731,30 +4735,30 @@
     <row r="14" spans="1:14" ht="24" customHeight="1"/>
     <row r="15" spans="1:14" ht="24" customHeight="1"/>
     <row r="16" spans="1:14" ht="24" customHeight="1"/>
-    <row r="17" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="18" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="19" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="20" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="21" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="22" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="23" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="24" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="25" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="26" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="27" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="28" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="29" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="30" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="31" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="32" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="33" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="34" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="35" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="36" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="37" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="38" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="39" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="40" s="3" customFormat="1" ht="24" customHeight="1"/>
+    <row r="17" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="18" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="19" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="20" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="21" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="22" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="23" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="24" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="25" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="26" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="27" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="28" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="29" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="30" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="31" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="32" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="33" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="34" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="35" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="36" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="37" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="38" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="39" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="40" s="1" customFormat="1" ht="24" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N2"/>
@@ -4769,47 +4773,47 @@
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="14" width="12" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3"/>
+    <col min="1" max="14" width="12" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1"/>
     <row r="4" spans="1:14" ht="24" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="5" t="s">
         <v>348</v>
       </c>
     </row>
@@ -4825,30 +4829,30 @@
     <row r="14" spans="1:14" ht="24" customHeight="1"/>
     <row r="15" spans="1:14" ht="24" customHeight="1"/>
     <row r="16" spans="1:14" ht="24" customHeight="1"/>
-    <row r="17" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="18" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="19" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="20" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="21" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="22" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="23" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="24" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="25" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="26" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="27" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="28" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="29" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="30" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="31" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="32" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="33" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="34" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="35" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="36" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="37" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="38" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="39" s="3" customFormat="1" ht="24" customHeight="1"/>
-    <row r="40" s="3" customFormat="1" ht="24" customHeight="1"/>
+    <row r="17" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="18" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="19" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="20" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="21" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="22" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="23" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="24" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="25" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="26" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="27" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="28" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="29" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="30" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="31" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="32" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="33" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="34" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="35" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="36" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="37" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="38" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="39" s="1" customFormat="1" ht="24" customHeight="1"/>
+    <row r="40" s="1" customFormat="1" ht="24" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N2"/>
